--- a/resumen_grupos_profesionales.xlsx
+++ b/resumen_grupos_profesionales.xlsx
@@ -460,10 +460,10 @@
         <v>490</v>
       </c>
       <c r="C2" t="n">
-        <v>1273.99</v>
+        <v>1213.32</v>
       </c>
       <c r="D2" t="n">
-        <v>49.09</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>318</v>
       </c>
       <c r="C3" t="n">
-        <v>1784.91</v>
+        <v>1724.55</v>
       </c>
       <c r="D3" t="n">
-        <v>47.82</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +492,10 @@
         <v>137</v>
       </c>
       <c r="C4" t="n">
-        <v>2334.98</v>
+        <v>2289.19</v>
       </c>
       <c r="D4" t="n">
-        <v>50.92</v>
+        <v>50.94</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         <v>55</v>
       </c>
       <c r="C5" t="n">
-        <v>3348.88</v>
+        <v>3100.82</v>
       </c>
       <c r="D5" t="n">
-        <v>44.95</v>
+        <v>44.96</v>
       </c>
     </row>
   </sheetData>
